--- a/output/10_Aviat_공급사회신_대조표.xlsx
+++ b/output/10_Aviat_공급사회신_대조표.xlsx
@@ -48,7 +48,7 @@
       <color rgb="000000FF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +68,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -121,6 +126,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2727,7 +2735,7 @@
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>변동, 공급사 확인 필요</t>
         </is>
@@ -3305,7 +3313,7 @@
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>변동, 공급사 확인 필요</t>
         </is>
@@ -3547,7 +3555,7 @@
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>변동, 공급사 확인 필요</t>
         </is>
@@ -3597,7 +3605,7 @@
           <t>참고 후보</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>변동, 공급사 확인 필요</t>
         </is>

--- a/output/10_Aviat_공급사회신_대조표.xlsx
+++ b/output/10_Aviat_공급사회신_대조표.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>발주이력상 관측 비율이 30% 이상 벌어져 대표 수량을 임의로 정하지 않은 품목이다. 이런 행은 수량 차이를 계산하지 않고 '내부 추정 변동(비교 보류)'로 표시한다 - 애니콤 회신 수량을 그대로 신뢰하고 참고용으로만 기록한다.</t>
+          <t>발주이력상 관측 비율이 30% 이상 벌어져 대표 수량을 임의로 정하지 않은 품목이다. 이런 행은 '내부 대표수량' 셀이 연한 빨간색으로 표시되어 있다 - 회신 입력 전부터 눈에 띄도록 고정 표시한 것이며, 04v2 파일과 동일한 색상 규칙이다. 이런 행은 수량 차이를 계산하지 않고 '내부 추정 변동(비교 보류)'로 표시한다 - 애니콤 회신 수량을 그대로 신뢰하고 참고용으로만 기록한다(내부 추정과 다르다고 '차이 있음'으로 오판하지 말 것).</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
